--- a/resources/templates/standard/L2300-02.xlsx
+++ b/resources/templates/standard/L2300-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>한도 견본표</t>
   </si>
@@ -634,12 +637,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -656,21 +661,21 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U1" s="3"/>
       <c r="V1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
@@ -741,14 +746,14 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -760,20 +765,20 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
       <c r="U4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
       <c r="X4" s="9"/>
       <c r="Y4" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="10"/>
       <c r="AA4" s="10"/>
@@ -867,13 +872,13 @@
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
       <c r="U7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z7" s="12"/>
       <c r="AA7" s="12"/>
@@ -947,7 +952,7 @@
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -964,7 +969,7 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
       <c r="P10" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q10" s="15"/>
       <c r="R10" s="15"/>
@@ -1015,7 +1020,7 @@
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -1032,7 +1037,7 @@
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
       <c r="P12" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="14" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -1100,7 +1105,7 @@
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
       <c r="P14" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
@@ -1151,7 +1156,7 @@
     </row>
     <row r="16" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -1168,7 +1173,7 @@
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
       <c r="P16" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
@@ -1219,7 +1224,7 @@
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -1236,7 +1241,7 @@
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
       <c r="P18" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="18"/>
       <c r="R18" s="18"/>
